--- a/Data/National Accounts/PSA-13TRD_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-13TRD_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CADA35-8D17-4343-99E6-560C81711B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B4EEF5-A533-414D-B89F-FEBED785E06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="TRD" sheetId="13" r:id="rId1"/>
@@ -685,10 +685,10 @@
     <t>Table 14.7 Gross Value Added in Wholesale and Retail Trade; Repair of Motor Vehicles and Motorcycles, by Industry</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -737,10 +737,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1205,7 +1207,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1215,7 +1217,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -2001,22 +2003,22 @@
         <v>157858.26166563126</v>
       </c>
       <c r="CV12" s="19">
-        <v>194932.73884800117</v>
+        <v>194999.20274009852</v>
       </c>
       <c r="CW12" s="19">
-        <v>273800.92722069391</v>
+        <v>271717.28231703106</v>
       </c>
       <c r="CX12" s="19">
-        <v>175156.58389910762</v>
+        <v>173621.21843411183</v>
       </c>
       <c r="CY12" s="19">
-        <v>162101.38934038067</v>
+        <v>160792.30260639059</v>
       </c>
       <c r="CZ12" s="19">
-        <v>204796.95195410814</v>
+        <v>205672.91213167578</v>
       </c>
       <c r="DA12" s="19">
-        <v>287861.49343887751</v>
+        <v>287839.75868115516</v>
       </c>
       <c r="DB12" s="8"/>
       <c r="DC12" s="8"/>
@@ -2392,22 +2394,22 @@
         <v>966511.85994364903</v>
       </c>
       <c r="CV13" s="19">
-        <v>1088018.7502523635</v>
+        <v>1087739.2264615209</v>
       </c>
       <c r="CW13" s="19">
-        <v>1121247.8452660744</v>
+        <v>1121824.5991160711</v>
       </c>
       <c r="CX13" s="19">
-        <v>876344.07257966325</v>
+        <v>877671.18625799485</v>
       </c>
       <c r="CY13" s="19">
-        <v>1032482.2891050226</v>
+        <v>1034056.1689891042</v>
       </c>
       <c r="CZ13" s="19">
-        <v>1153011.4115316775</v>
+        <v>1152395.8025740362</v>
       </c>
       <c r="DA13" s="19">
-        <v>1185455.7723050781</v>
+        <v>1186549.4206410318</v>
       </c>
       <c r="DB13" s="8"/>
       <c r="DC13" s="8"/>
@@ -2786,19 +2788,19 @@
         <v>30473.238410368398</v>
       </c>
       <c r="CW14" s="19">
-        <v>31830.157533077287</v>
+        <v>31918.148962389576</v>
       </c>
       <c r="CX14" s="19">
-        <v>31622.016926876073</v>
+        <v>31532.981500690283</v>
       </c>
       <c r="CY14" s="19">
-        <v>21203.133404727276</v>
+        <v>21082.417102666837</v>
       </c>
       <c r="CZ14" s="19">
-        <v>32873.197735588299</v>
+        <v>32907.742918805772</v>
       </c>
       <c r="DA14" s="19">
-        <v>34648.638906174645</v>
+        <v>33714.837790068879</v>
       </c>
       <c r="DB14" s="8"/>
       <c r="DC14" s="8"/>
@@ -3354,22 +3356,22 @@
         <v>1143804.6270750547</v>
       </c>
       <c r="CV16" s="20">
-        <v>1313424.7275107331</v>
+        <v>1313211.6676119878</v>
       </c>
       <c r="CW16" s="20">
-        <v>1426878.9300198455</v>
+        <v>1425460.030395492</v>
       </c>
       <c r="CX16" s="20">
-        <v>1083122.6734056468</v>
+        <v>1082825.386192797</v>
       </c>
       <c r="CY16" s="20">
-        <v>1215786.8118501306</v>
+        <v>1215930.8886981616</v>
       </c>
       <c r="CZ16" s="20">
-        <v>1390681.561221374</v>
+        <v>1390976.4576245176</v>
       </c>
       <c r="DA16" s="20">
-        <v>1507965.9046501301</v>
+        <v>1508104.0171122558</v>
       </c>
       <c r="DB16" s="8"/>
       <c r="DC16" s="8"/>
@@ -3930,7 +3932,7 @@
     </row>
     <row r="23" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:179" x14ac:dyDescent="0.2">
@@ -3940,7 +3942,7 @@
     </row>
     <row r="26" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:179" x14ac:dyDescent="0.2">
@@ -4726,22 +4728,22 @@
         <v>132750.52359066412</v>
       </c>
       <c r="CV32" s="19">
-        <v>160410.79425667468</v>
+        <v>160465.57594159569</v>
       </c>
       <c r="CW32" s="19">
-        <v>219365.64211005261</v>
+        <v>217697.58109104767</v>
       </c>
       <c r="CX32" s="19">
-        <v>139805.81334557943</v>
+        <v>138581.31303223345</v>
       </c>
       <c r="CY32" s="19">
-        <v>131779.60135097086</v>
+        <v>130715.38513023988</v>
       </c>
       <c r="CZ32" s="19">
-        <v>163236.84189228172</v>
+        <v>163936.16961152005</v>
       </c>
       <c r="DA32" s="19">
-        <v>224878.96417628563</v>
+        <v>224996.1327759999</v>
       </c>
       <c r="DB32" s="8"/>
       <c r="DC32" s="8"/>
@@ -5117,22 +5119,22 @@
         <v>805670.28401699965</v>
       </c>
       <c r="CV33" s="19">
-        <v>930545.60788527806</v>
+        <v>930306.67349702888</v>
       </c>
       <c r="CW33" s="19">
-        <v>954791.17130854283</v>
+        <v>955280.61859403155</v>
       </c>
       <c r="CX33" s="19">
-        <v>737084.04194265581</v>
+        <v>738210.19278089982</v>
       </c>
       <c r="CY33" s="19">
-        <v>855620.70867376192</v>
+        <v>856924.9869514578</v>
       </c>
       <c r="CZ33" s="19">
-        <v>981794.94383922871</v>
+        <v>981271.0512758086</v>
       </c>
       <c r="DA33" s="19">
-        <v>1002182.5464835169</v>
+        <v>1003131.8415263239</v>
       </c>
       <c r="DB33" s="8"/>
       <c r="DC33" s="8"/>
@@ -5511,19 +5513,19 @@
         <v>29745.490233338191</v>
       </c>
       <c r="CW34" s="19">
-        <v>30624.415059308398</v>
+        <v>30708.916529346112</v>
       </c>
       <c r="CX34" s="19">
-        <v>29269.781197498447</v>
+        <v>29187.464417945055</v>
       </c>
       <c r="CY34" s="19">
-        <v>20229.934000849436</v>
+        <v>20114.78764220473</v>
       </c>
       <c r="CZ34" s="19">
-        <v>31611.328284905692</v>
+        <v>31644.547810125114</v>
       </c>
       <c r="DA34" s="19">
-        <v>32809.713129845608</v>
+        <v>31929.635513315559</v>
       </c>
       <c r="DB34" s="8"/>
       <c r="DC34" s="8"/>
@@ -6079,22 +6081,22 @@
         <v>957170.56561870489</v>
       </c>
       <c r="CV36" s="20">
-        <v>1120701.8923752909</v>
+        <v>1120517.7396719628</v>
       </c>
       <c r="CW36" s="20">
-        <v>1204781.2284779036</v>
+        <v>1203687.1162144253</v>
       </c>
       <c r="CX36" s="20">
-        <v>906159.63648573367</v>
+        <v>905978.97023107822</v>
       </c>
       <c r="CY36" s="20">
-        <v>1007630.2440255822</v>
+        <v>1007755.1597239025</v>
       </c>
       <c r="CZ36" s="20">
-        <v>1176643.1140164162</v>
+        <v>1176851.7686974539</v>
       </c>
       <c r="DA36" s="20">
-        <v>1259871.2237896482</v>
+        <v>1260057.6098156394</v>
       </c>
       <c r="DB36" s="8"/>
       <c r="DC36" s="8"/>
@@ -6659,7 +6661,7 @@
     </row>
     <row r="43" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CX43" s="4"/>
       <c r="CY43" s="4"/>
@@ -6687,7 +6689,7 @@
     </row>
     <row r="46" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CX46" s="4"/>
       <c r="CY46" s="4"/>
@@ -7469,22 +7471,22 @@
         <v>6.8636165314617443</v>
       </c>
       <c r="CR52" s="16">
-        <v>6.1421692810638575</v>
+        <v>6.1783593111622821</v>
       </c>
       <c r="CS52" s="16">
-        <v>5.8944485613958761</v>
+        <v>5.0885841316772371</v>
       </c>
       <c r="CT52" s="16">
-        <v>9.1795590962593394</v>
+        <v>8.2225267039376178</v>
       </c>
       <c r="CU52" s="16">
-        <v>2.6879351324272278</v>
+        <v>1.8586552960871359</v>
       </c>
       <c r="CV52" s="16">
-        <v>5.060316273398584</v>
+        <v>5.4737195032553672</v>
       </c>
       <c r="CW52" s="16">
-        <v>5.1353245443359157</v>
+        <v>5.9335483656549002</v>
       </c>
       <c r="CX52" s="18"/>
       <c r="CY52" s="18"/>
@@ -7848,22 +7850,22 @@
         <v>12.730991863342837</v>
       </c>
       <c r="CR53" s="16">
-        <v>8.8956767652108084</v>
+        <v>8.8677002874444781</v>
       </c>
       <c r="CS53" s="16">
-        <v>8.6825136891341685</v>
+        <v>8.7384184192633683</v>
       </c>
       <c r="CT53" s="16">
-        <v>9.1495640046909585</v>
+        <v>9.3148573910524846</v>
       </c>
       <c r="CU53" s="16">
-        <v>6.8256202427996868</v>
+        <v>6.9884614814134949</v>
       </c>
       <c r="CV53" s="16">
-        <v>5.9734872458989514</v>
+        <v>5.9441247074307313</v>
       </c>
       <c r="CW53" s="16">
-        <v>5.7264704953584129</v>
+        <v>5.7696026255762263</v>
       </c>
       <c r="CX53" s="18"/>
       <c r="CY53" s="18"/>
@@ -8230,19 +8232,19 @@
         <v>6.1575824474803227</v>
       </c>
       <c r="CS54" s="16">
-        <v>6.6669495016198539</v>
+        <v>6.9618200921054836</v>
       </c>
       <c r="CT54" s="16">
-        <v>7.7996613477822478</v>
+        <v>7.496139000900385</v>
       </c>
       <c r="CU54" s="16">
-        <v>9.1004525022138267</v>
+        <v>8.4793083096176929</v>
       </c>
       <c r="CV54" s="16">
-        <v>7.8756294060408294</v>
+        <v>7.9889917692798917</v>
       </c>
       <c r="CW54" s="16">
-        <v>8.8547515674983543</v>
+        <v>5.6290508255864466</v>
       </c>
       <c r="CX54" s="18"/>
       <c r="CY54" s="18"/>
@@ -8782,22 +8784,22 @@
         <v>11.904397077309369</v>
       </c>
       <c r="CR56" s="16">
-        <v>8.4133912633538728</v>
+        <v>8.3958047616827969</v>
       </c>
       <c r="CS56" s="16">
-        <v>8.0908583732078228</v>
+        <v>7.9833719739660296</v>
       </c>
       <c r="CT56" s="16">
-        <v>9.1145203322933384</v>
+        <v>9.0845714147537819</v>
       </c>
       <c r="CU56" s="16">
-        <v>6.2932237788851495</v>
+        <v>6.3058200601573589</v>
       </c>
       <c r="CV56" s="16">
-        <v>5.8820906971244398</v>
+        <v>5.9217254864892652</v>
       </c>
       <c r="CW56" s="16">
-        <v>5.6828209404673657</v>
+        <v>5.7977063512495874</v>
       </c>
       <c r="CX56" s="18"/>
       <c r="CY56" s="18"/>
@@ -9362,7 +9364,7 @@
     </row>
     <row r="63" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CX63" s="4"/>
       <c r="CY63" s="4"/>
@@ -9386,7 +9388,7 @@
     </row>
     <row r="66" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CX66" s="4"/>
       <c r="CY66" s="4"/>
@@ -10168,22 +10170,22 @@
         <v>4.1108900636538976</v>
       </c>
       <c r="CR72" s="16">
-        <v>3.5963919124509545</v>
+        <v>3.6317709835851559</v>
       </c>
       <c r="CS72" s="16">
-        <v>3.4225770590495586</v>
+        <v>2.636149578347343</v>
       </c>
       <c r="CT72" s="16">
-        <v>5.563758127450285</v>
+        <v>4.6391695727131292</v>
       </c>
       <c r="CU72" s="16">
-        <v>-0.73138863292705025</v>
+        <v>-1.5330549404833818</v>
       </c>
       <c r="CV72" s="16">
-        <v>1.7617565256145156</v>
+        <v>2.1628275407727102</v>
       </c>
       <c r="CW72" s="16">
-        <v>2.5133024539308053</v>
+        <v>3.3526103727812</v>
       </c>
       <c r="CX72" s="18"/>
       <c r="CY72" s="18"/>
@@ -10547,22 +10549,22 @@
         <v>5.9322290752709819</v>
       </c>
       <c r="CR73" s="16">
-        <v>5.2439154036335367</v>
+        <v>5.2168921279006355</v>
       </c>
       <c r="CS73" s="16">
-        <v>5.8328331056811891</v>
+        <v>5.8870853803520475</v>
       </c>
       <c r="CT73" s="16">
-        <v>6.5073656963862732</v>
+        <v>6.6700925393688095</v>
       </c>
       <c r="CU73" s="16">
-        <v>6.1998593776742013</v>
+        <v>6.3617467283150688</v>
       </c>
       <c r="CV73" s="16">
-        <v>5.5074502012231221</v>
+        <v>5.4782341383410937</v>
       </c>
       <c r="CW73" s="16">
-        <v>4.9635330320476356</v>
+        <v>5.0091273706273967</v>
       </c>
       <c r="CX73" s="18"/>
       <c r="CY73" s="18"/>
@@ -10929,19 +10931,19 @@
         <v>5.0379422229693631</v>
       </c>
       <c r="CS74" s="16">
-        <v>5.6209673521601786</v>
+        <v>5.912405637292423</v>
       </c>
       <c r="CT74" s="16">
-        <v>7.1000528958612676</v>
+        <v>6.7988503899423165</v>
       </c>
       <c r="CU74" s="16">
-        <v>7.8943738310475453</v>
+        <v>7.2802519923715465</v>
       </c>
       <c r="CV74" s="16">
-        <v>6.2726754103931626</v>
+        <v>6.384354609353494</v>
       </c>
       <c r="CW74" s="16">
-        <v>7.1358034636909196</v>
+        <v>3.9751287962338324</v>
       </c>
       <c r="CX74" s="18"/>
       <c r="CY74" s="18"/>
@@ -11481,22 +11483,22 @@
         <v>5.8011847796697396</v>
       </c>
       <c r="CR76" s="16">
-        <v>4.9994397411558396</v>
+        <v>4.9821863298715243</v>
       </c>
       <c r="CS76" s="16">
-        <v>5.3802951036789466</v>
+        <v>5.2845948466724764</v>
       </c>
       <c r="CT76" s="16">
-        <v>6.3796726068551948</v>
+        <v>6.3584630801365876</v>
       </c>
       <c r="CU76" s="16">
-        <v>5.2717540864057639</v>
+        <v>5.2848046024587205</v>
       </c>
       <c r="CV76" s="16">
-        <v>4.9916237334586668</v>
+        <v>5.0274999699677352</v>
       </c>
       <c r="CW76" s="16">
-        <v>4.572614015686824</v>
+        <v>4.6831516963061262</v>
       </c>
       <c r="CX76" s="18"/>
       <c r="CY76" s="18"/>
@@ -12048,7 +12050,7 @@
     </row>
     <row r="82" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84" spans="1:179" x14ac:dyDescent="0.2">
@@ -12058,7 +12060,7 @@
     </row>
     <row r="85" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="86" spans="1:179" x14ac:dyDescent="0.2">
@@ -12844,22 +12846,22 @@
         <v>118.91347574069597</v>
       </c>
       <c r="CV91" s="16">
-        <v>121.52096107453194</v>
+        <v>121.52089418298164</v>
       </c>
       <c r="CW91" s="16">
-        <v>124.81486370747699</v>
+        <v>124.81410264425065</v>
       </c>
       <c r="CX91" s="16">
-        <v>125.28562275600534</v>
+        <v>125.28472608260554</v>
       </c>
       <c r="CY91" s="16">
         <v>123.00947011415924</v>
       </c>
       <c r="CZ91" s="16">
-        <v>125.46000619716197</v>
+        <v>125.45914218873078</v>
       </c>
       <c r="DA91" s="16">
-        <v>128.00730139134714</v>
+        <v>127.93098047054909</v>
       </c>
       <c r="DB91" s="8"/>
       <c r="DC91" s="8"/>
@@ -13235,22 +13237,22 @@
         <v>119.96369719939375</v>
       </c>
       <c r="CV92" s="16">
-        <v>116.92266784483061</v>
+        <v>116.92265114821782</v>
       </c>
       <c r="CW92" s="16">
-        <v>117.43383045000326</v>
+        <v>117.43403742108332</v>
       </c>
       <c r="CX92" s="16">
-        <v>118.89337208684836</v>
+        <v>118.89177294501093</v>
       </c>
       <c r="CY92" s="16">
         <v>120.67055865272376</v>
       </c>
       <c r="CZ92" s="16">
-        <v>117.43912705670705</v>
+        <v>117.43909097040397</v>
       </c>
       <c r="DA92" s="16">
-        <v>118.28740946094449</v>
+        <v>118.28449377457974</v>
       </c>
       <c r="DB92" s="8"/>
       <c r="DC92" s="8"/>
@@ -13629,19 +13631,19 @@
         <v>102.44658323437064</v>
       </c>
       <c r="CW93" s="16">
-        <v>103.93719348250016</v>
+        <v>103.93772418472626</v>
       </c>
       <c r="CX93" s="16">
-        <v>108.03639669700932</v>
+        <v>108.03604262829749</v>
       </c>
       <c r="CY93" s="16">
-        <v>104.81068995992264</v>
+        <v>104.81053778779068</v>
       </c>
       <c r="CZ93" s="16">
-        <v>103.99182672524756</v>
+        <v>103.99182543628093</v>
       </c>
       <c r="DA93" s="16">
-        <v>105.60482125842255</v>
+        <v>105.59105122264501</v>
       </c>
       <c r="DB93" s="8"/>
       <c r="DC93" s="8"/>
@@ -14197,22 +14199,22 @@
         <v>119.49851658212154</v>
       </c>
       <c r="CV95" s="16">
-        <v>117.19661905156353</v>
+        <v>117.19686544154465</v>
       </c>
       <c r="CW95" s="16">
-        <v>118.43469140223372</v>
+        <v>118.42446522801859</v>
       </c>
       <c r="CX95" s="16">
-        <v>119.52890305357352</v>
+        <v>119.51992505042502</v>
       </c>
       <c r="CY95" s="16">
-        <v>120.65803096510305</v>
+        <v>120.6573716805671</v>
       </c>
       <c r="CZ95" s="16">
-        <v>118.19060041700729</v>
+        <v>118.19470341316291</v>
       </c>
       <c r="DA95" s="16">
-        <v>119.69206663155794</v>
+        <v>119.68532274749791</v>
       </c>
       <c r="DB95" s="8"/>
       <c r="DC95" s="8"/>
@@ -14413,7 +14415,7 @@
     </row>
     <row r="102" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="104" spans="1:179" x14ac:dyDescent="0.2">
@@ -14423,7 +14425,7 @@
     </row>
     <row r="105" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="106" spans="1:179" x14ac:dyDescent="0.2">
@@ -15209,22 +15211,22 @@
         <v>13.801156065376963</v>
       </c>
       <c r="CV111" s="16">
-        <v>14.841561512051571</v>
+        <v>14.849030628451176</v>
       </c>
       <c r="CW111" s="16">
-        <v>19.188798815389742</v>
+        <v>19.061725795401184</v>
       </c>
       <c r="CX111" s="16">
-        <v>16.17144467564005</v>
+        <v>16.034091982693745</v>
       </c>
       <c r="CY111" s="16">
-        <v>13.333043898847855</v>
+        <v>13.223802775381676</v>
       </c>
       <c r="CZ111" s="16">
-        <v>14.726372856647647</v>
+        <v>14.786225245172011</v>
       </c>
       <c r="DA111" s="16">
-        <v>19.089390055252313</v>
+        <v>19.086200647639398</v>
       </c>
       <c r="DB111" s="8"/>
       <c r="DC111" s="8"/>
@@ -15600,22 +15602,22 @@
         <v>84.499733351771795</v>
       </c>
       <c r="CV112" s="16">
-        <v>82.838302604095944</v>
+        <v>82.830457061009994</v>
       </c>
       <c r="CW112" s="16">
-        <v>78.580447273860841</v>
+        <v>78.699126962179534</v>
       </c>
       <c r="CX112" s="16">
-        <v>80.909032198927875</v>
+        <v>81.05380585358067</v>
       </c>
       <c r="CY112" s="16">
-        <v>84.9229716132417</v>
+        <v>85.042347274870053</v>
       </c>
       <c r="CZ112" s="16">
-        <v>82.909807944748948</v>
+        <v>82.847973181521368</v>
       </c>
       <c r="DA112" s="16">
-        <v>78.61290289452009</v>
+        <v>78.678221606561166</v>
       </c>
       <c r="DB112" s="8"/>
       <c r="DC112" s="8"/>
@@ -15991,22 +15993,22 @@
         <v>1.6991105828512327</v>
       </c>
       <c r="CV113" s="16">
-        <v>2.320135883852497</v>
+        <v>2.320512310538827</v>
       </c>
       <c r="CW113" s="16">
-        <v>2.230753910749427</v>
+        <v>2.2391472424192722</v>
       </c>
       <c r="CX113" s="16">
-        <v>2.9195231254320833</v>
+        <v>2.9121021637255775</v>
       </c>
       <c r="CY113" s="16">
-        <v>1.7439844879104494</v>
+        <v>1.7338499497482758</v>
       </c>
       <c r="CZ113" s="16">
-        <v>2.3638191986033976</v>
+        <v>2.3658015733066375</v>
       </c>
       <c r="DA113" s="16">
-        <v>2.2977070502276131</v>
+        <v>2.2355777457994339</v>
       </c>
       <c r="DB113" s="8"/>
       <c r="DC113" s="8"/>
@@ -17138,7 +17140,7 @@
     </row>
     <row r="122" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="124" spans="1:179" x14ac:dyDescent="0.2">
@@ -17148,7 +17150,7 @@
     </row>
     <row r="125" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="126" spans="1:179" x14ac:dyDescent="0.2">
@@ -17934,22 +17936,22 @@
         <v>13.86905619113513</v>
       </c>
       <c r="CV131" s="16">
-        <v>14.313422271170548</v>
+        <v>14.320663587938625</v>
       </c>
       <c r="CW131" s="16">
-        <v>18.207923307968098</v>
+        <v>18.085894428753438</v>
       </c>
       <c r="CX131" s="16">
-        <v>15.428386756198281</v>
+        <v>15.296305718540799</v>
       </c>
       <c r="CY131" s="16">
-        <v>13.07817050275291</v>
+        <v>12.970946749213603</v>
       </c>
       <c r="CZ131" s="16">
-        <v>13.873097113965201</v>
+        <v>13.930061029943092</v>
       </c>
       <c r="DA131" s="16">
-        <v>17.849361103737067</v>
+        <v>17.856019520323311</v>
       </c>
       <c r="DB131" s="8"/>
       <c r="DC131" s="8"/>
@@ -18325,22 +18327,22 @@
         <v>84.172070575135479</v>
       </c>
       <c r="CV132" s="16">
-        <v>83.032393736127034</v>
+        <v>83.024716214611729</v>
       </c>
       <c r="CW132" s="16">
-        <v>79.250169967771384</v>
+        <v>79.362868117951805</v>
       </c>
       <c r="CX132" s="16">
-        <v>81.341522206971561</v>
+        <v>81.48204506254848</v>
       </c>
       <c r="CY132" s="16">
-        <v>84.914155142413421</v>
+        <v>85.033053781260918</v>
       </c>
       <c r="CZ132" s="16">
-        <v>83.440333958860109</v>
+        <v>83.381023623891465</v>
       </c>
       <c r="DA132" s="16">
-        <v>79.546427250634963</v>
+        <v>79.609998281990727</v>
       </c>
       <c r="DB132" s="8"/>
       <c r="DC132" s="8"/>
@@ -18716,22 +18718,22 @@
         <v>1.9588732337293955</v>
       </c>
       <c r="CV133" s="16">
-        <v>2.6541839927024307</v>
+        <v>2.6546201974496477</v>
       </c>
       <c r="CW133" s="16">
-        <v>2.5419067242605253</v>
+        <v>2.5512374532947657</v>
       </c>
       <c r="CX133" s="16">
-        <v>3.2300910368301605</v>
+        <v>3.2216492189107355</v>
       </c>
       <c r="CY133" s="16">
-        <v>2.0076743548336595</v>
+        <v>1.9959994695254784</v>
       </c>
       <c r="CZ133" s="16">
-        <v>2.6865689271746893</v>
+        <v>2.6889153461654285</v>
       </c>
       <c r="DA133" s="16">
-        <v>2.6042116456279674</v>
+        <v>2.5339821976859636</v>
       </c>
       <c r="DB133" s="8"/>
       <c r="DC133" s="8"/>

--- a/Data/National Accounts/PSA-13TRD_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-13TRD_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B4EEF5-A533-414D-B89F-FEBED785E06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF82A430-A3B6-4809-ADBA-03A8B71168F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="TRD" sheetId="13" r:id="rId1"/>
@@ -353,7 +353,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">TRD!$A$1:$DA$138</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">TRD!$A$1:$DB$138</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -527,7 +527,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="55">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -685,10 +685,13 @@
     <t>Table 14.7 Gross Value Added in Wholesale and Retail Trade; Repair of Motor Vehicles and Motorcycles, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of May 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>Q1 2000 to Q1 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1191,8 +1194,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="59.28515625" style="3" customWidth="1"/>
-    <col min="2" max="105" width="13" style="3" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="3"/>
+    <col min="2" max="106" width="13" style="3" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1207,7 +1210,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1217,7 +1220,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -1383,6 +1386,9 @@
       <c r="CY9" s="21"/>
       <c r="CZ9" s="21"/>
       <c r="DA9" s="21"/>
+      <c r="DB9" s="21">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1699,6 +1705,9 @@
       </c>
       <c r="DA10" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2020,7 +2029,9 @@
       <c r="DA12" s="19">
         <v>287839.75868115516</v>
       </c>
-      <c r="DB12" s="8"/>
+      <c r="DB12" s="19">
+        <v>178771.70160681123</v>
+      </c>
       <c r="DC12" s="8"/>
       <c r="DD12" s="8"/>
       <c r="DE12" s="8"/>
@@ -2411,7 +2422,9 @@
       <c r="DA13" s="19">
         <v>1186549.4206410318</v>
       </c>
-      <c r="DB13" s="8"/>
+      <c r="DB13" s="19">
+        <v>944364.16344454163</v>
+      </c>
       <c r="DC13" s="8"/>
       <c r="DD13" s="8"/>
       <c r="DE13" s="8"/>
@@ -2802,7 +2815,9 @@
       <c r="DA14" s="19">
         <v>33714.837790068879</v>
       </c>
-      <c r="DB14" s="8"/>
+      <c r="DB14" s="19">
+        <v>32451.80003825172</v>
+      </c>
       <c r="DC14" s="8"/>
       <c r="DD14" s="8"/>
       <c r="DE14" s="8"/>
@@ -3373,7 +3388,9 @@
       <c r="DA16" s="20">
         <v>1508104.0171122558</v>
       </c>
-      <c r="DB16" s="8"/>
+      <c r="DB16" s="20">
+        <v>1155587.6650896047</v>
+      </c>
       <c r="DC16" s="8"/>
       <c r="DD16" s="8"/>
       <c r="DE16" s="8"/>
@@ -3554,6 +3571,7 @@
       <c r="CY17" s="10"/>
       <c r="CZ17" s="10"/>
       <c r="DA17" s="10"/>
+      <c r="DB17" s="10"/>
     </row>
     <row r="18" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
@@ -3932,7 +3950,7 @@
     </row>
     <row r="23" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:179" x14ac:dyDescent="0.2">
@@ -3942,7 +3960,7 @@
     </row>
     <row r="26" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:179" x14ac:dyDescent="0.2">
@@ -4108,6 +4126,9 @@
       <c r="CY29" s="21"/>
       <c r="CZ29" s="21"/>
       <c r="DA29" s="21"/>
+      <c r="DB29" s="21">
+        <v>2026</v>
+      </c>
     </row>
     <row r="30" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
@@ -4424,6 +4445,9 @@
       </c>
       <c r="DA30" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB30" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -4745,7 +4769,9 @@
       <c r="DA32" s="19">
         <v>224996.1327759999</v>
       </c>
-      <c r="DB32" s="8"/>
+      <c r="DB32" s="19">
+        <v>139913.92417497106</v>
+      </c>
       <c r="DC32" s="8"/>
       <c r="DD32" s="8"/>
       <c r="DE32" s="8"/>
@@ -5136,7 +5162,9 @@
       <c r="DA33" s="19">
         <v>1003131.8415263239</v>
       </c>
-      <c r="DB33" s="8"/>
+      <c r="DB33" s="19">
+        <v>777925.55523356819</v>
+      </c>
       <c r="DC33" s="8"/>
       <c r="DD33" s="8"/>
       <c r="DE33" s="8"/>
@@ -5527,7 +5555,9 @@
       <c r="DA34" s="19">
         <v>31929.635513315559</v>
       </c>
-      <c r="DB34" s="8"/>
+      <c r="DB34" s="19">
+        <v>29633.537430457443</v>
+      </c>
       <c r="DC34" s="8"/>
       <c r="DD34" s="8"/>
       <c r="DE34" s="8"/>
@@ -5707,7 +5737,7 @@
       <c r="CY35" s="20"/>
       <c r="CZ35" s="20"/>
       <c r="DA35" s="20"/>
-      <c r="DB35" s="8"/>
+      <c r="DB35" s="20"/>
       <c r="DC35" s="8"/>
       <c r="DD35" s="8"/>
       <c r="DE35" s="8"/>
@@ -6098,7 +6128,9 @@
       <c r="DA36" s="20">
         <v>1260057.6098156394</v>
       </c>
-      <c r="DB36" s="8"/>
+      <c r="DB36" s="20">
+        <v>947473.01683899667</v>
+      </c>
       <c r="DC36" s="8"/>
       <c r="DD36" s="8"/>
       <c r="DE36" s="8"/>
@@ -6279,6 +6311,7 @@
       <c r="CY37" s="10"/>
       <c r="CZ37" s="10"/>
       <c r="DA37" s="10"/>
+      <c r="DB37" s="10"/>
     </row>
     <row r="38" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
@@ -6658,15 +6691,17 @@
       <c r="CY42" s="4"/>
       <c r="CZ42" s="4"/>
       <c r="DA42" s="4"/>
+      <c r="DB42" s="4"/>
     </row>
     <row r="43" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CX43" s="4"/>
       <c r="CY43" s="4"/>
       <c r="CZ43" s="4"/>
       <c r="DA43" s="4"/>
+      <c r="DB43" s="4"/>
     </row>
     <row r="44" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT44" s="6"/>
@@ -6677,6 +6712,7 @@
       <c r="CY44" s="4"/>
       <c r="CZ44" s="4"/>
       <c r="DA44" s="4"/>
+      <c r="DB44" s="4"/>
     </row>
     <row r="45" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
@@ -6686,15 +6722,17 @@
       <c r="CY45" s="4"/>
       <c r="CZ45" s="4"/>
       <c r="DA45" s="4"/>
+      <c r="DB45" s="4"/>
     </row>
     <row r="46" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CX46" s="4"/>
       <c r="CY46" s="4"/>
       <c r="CZ46" s="4"/>
       <c r="DA46" s="4"/>
+      <c r="DB46" s="4"/>
     </row>
     <row r="47" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
@@ -6704,12 +6742,14 @@
       <c r="CY47" s="4"/>
       <c r="CZ47" s="4"/>
       <c r="DA47" s="4"/>
+      <c r="DB47" s="4"/>
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CX48" s="4"/>
       <c r="CY48" s="4"/>
       <c r="CZ48" s="4"/>
       <c r="DA48" s="4"/>
+      <c r="DB48" s="4"/>
     </row>
     <row r="49" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="17"/>
@@ -6863,10 +6903,13 @@
       <c r="CU49" s="21"/>
       <c r="CV49" s="21"/>
       <c r="CW49" s="21"/>
-      <c r="CX49" s="22"/>
+      <c r="CX49" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="CY49" s="22"/>
       <c r="CZ49" s="22"/>
       <c r="DA49" s="22"/>
+      <c r="DB49" s="22"/>
     </row>
     <row r="50" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
@@ -7172,17 +7215,20 @@
       <c r="CW50" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX50" s="23"/>
+      <c r="CX50" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY50" s="23"/>
       <c r="CZ50" s="23"/>
       <c r="DA50" s="23"/>
+      <c r="DB50" s="23"/>
     </row>
     <row r="51" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6"/>
-      <c r="CX51" s="4"/>
       <c r="CY51" s="4"/>
       <c r="CZ51" s="4"/>
       <c r="DA51" s="4"/>
+      <c r="DB51" s="4"/>
     </row>
     <row r="52" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
@@ -7488,11 +7534,13 @@
       <c r="CW52" s="16">
         <v>5.9335483656549002</v>
       </c>
-      <c r="CX52" s="18"/>
+      <c r="CX52" s="16">
+        <v>2.9665056029162429</v>
+      </c>
       <c r="CY52" s="18"/>
       <c r="CZ52" s="18"/>
       <c r="DA52" s="18"/>
-      <c r="DB52" s="8"/>
+      <c r="DB52" s="18"/>
       <c r="DC52" s="8"/>
       <c r="DD52" s="8"/>
       <c r="DE52" s="8"/>
@@ -7867,11 +7915,13 @@
       <c r="CW53" s="16">
         <v>5.7696026255762263</v>
       </c>
-      <c r="CX53" s="18"/>
+      <c r="CX53" s="16">
+        <v>7.5988568647099299</v>
+      </c>
       <c r="CY53" s="18"/>
       <c r="CZ53" s="18"/>
       <c r="DA53" s="18"/>
-      <c r="DB53" s="8"/>
+      <c r="DB53" s="18"/>
       <c r="DC53" s="8"/>
       <c r="DD53" s="8"/>
       <c r="DE53" s="8"/>
@@ -8246,11 +8296,13 @@
       <c r="CW54" s="16">
         <v>5.6290508255864466</v>
       </c>
-      <c r="CX54" s="18"/>
+      <c r="CX54" s="16">
+        <v>2.9138333701217647</v>
+      </c>
       <c r="CY54" s="18"/>
       <c r="CZ54" s="18"/>
       <c r="DA54" s="18"/>
-      <c r="DB54" s="8"/>
+      <c r="DB54" s="18"/>
       <c r="DC54" s="8"/>
       <c r="DD54" s="8"/>
       <c r="DE54" s="8"/>
@@ -8422,11 +8474,11 @@
       <c r="CU55" s="8"/>
       <c r="CV55" s="8"/>
       <c r="CW55" s="8"/>
-      <c r="CX55" s="7"/>
+      <c r="CX55" s="8"/>
       <c r="CY55" s="7"/>
       <c r="CZ55" s="7"/>
       <c r="DA55" s="7"/>
-      <c r="DB55" s="8"/>
+      <c r="DB55" s="7"/>
       <c r="DC55" s="8"/>
       <c r="DD55" s="8"/>
       <c r="DE55" s="8"/>
@@ -8801,11 +8853,13 @@
       <c r="CW56" s="16">
         <v>5.7977063512495874</v>
       </c>
-      <c r="CX56" s="18"/>
+      <c r="CX56" s="16">
+        <v>6.7196687318755295</v>
+      </c>
       <c r="CY56" s="18"/>
       <c r="CZ56" s="18"/>
       <c r="DA56" s="18"/>
-      <c r="DB56" s="8"/>
+      <c r="DB56" s="18"/>
       <c r="DC56" s="8"/>
       <c r="DD56" s="8"/>
       <c r="DE56" s="8"/>
@@ -8978,19 +9032,20 @@
       <c r="CU57" s="10"/>
       <c r="CV57" s="10"/>
       <c r="CW57" s="10"/>
-      <c r="CX57" s="24"/>
+      <c r="CX57" s="10"/>
       <c r="CY57" s="24"/>
       <c r="CZ57" s="24"/>
       <c r="DA57" s="24"/>
+      <c r="DB57" s="24"/>
     </row>
     <row r="58" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A58" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CX58" s="4"/>
       <c r="CY58" s="4"/>
       <c r="CZ58" s="4"/>
       <c r="DA58" s="4"/>
+      <c r="DB58" s="4"/>
     </row>
     <row r="59" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="8"/>
@@ -9093,11 +9148,11 @@
       <c r="CU59" s="8"/>
       <c r="CV59" s="8"/>
       <c r="CW59" s="8"/>
-      <c r="CX59" s="7"/>
+      <c r="CX59" s="8"/>
       <c r="CY59" s="7"/>
       <c r="CZ59" s="7"/>
       <c r="DA59" s="7"/>
-      <c r="DB59" s="8"/>
+      <c r="DB59" s="7"/>
       <c r="DC59" s="8"/>
       <c r="DD59" s="8"/>
       <c r="DE59" s="8"/>
@@ -9269,11 +9324,11 @@
       <c r="CU60" s="8"/>
       <c r="CV60" s="8"/>
       <c r="CW60" s="8"/>
-      <c r="CX60" s="7"/>
+      <c r="CX60" s="8"/>
       <c r="CY60" s="7"/>
       <c r="CZ60" s="7"/>
       <c r="DA60" s="7"/>
-      <c r="DB60" s="8"/>
+      <c r="DB60" s="7"/>
       <c r="DC60" s="8"/>
       <c r="DD60" s="8"/>
       <c r="DE60" s="8"/>
@@ -9348,67 +9403,67 @@
       <c r="A61" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="CX61" s="4"/>
       <c r="CY61" s="4"/>
       <c r="CZ61" s="4"/>
       <c r="DA61" s="4"/>
+      <c r="DB61" s="4"/>
     </row>
     <row r="62" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="CX62" s="4"/>
       <c r="CY62" s="4"/>
       <c r="CZ62" s="4"/>
       <c r="DA62" s="4"/>
+      <c r="DB62" s="4"/>
     </row>
     <row r="63" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="CX63" s="4"/>
+        <v>52</v>
+      </c>
       <c r="CY63" s="4"/>
       <c r="CZ63" s="4"/>
       <c r="DA63" s="4"/>
+      <c r="DB63" s="4"/>
     </row>
     <row r="64" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX64" s="4"/>
       <c r="CY64" s="4"/>
       <c r="CZ64" s="4"/>
       <c r="DA64" s="4"/>
+      <c r="DB64" s="4"/>
     </row>
     <row r="65" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="CX65" s="4"/>
       <c r="CY65" s="4"/>
       <c r="CZ65" s="4"/>
       <c r="DA65" s="4"/>
+      <c r="DB65" s="4"/>
     </row>
     <row r="66" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="CX66" s="4"/>
+        <v>53</v>
+      </c>
       <c r="CY66" s="4"/>
       <c r="CZ66" s="4"/>
       <c r="DA66" s="4"/>
+      <c r="DB66" s="4"/>
     </row>
     <row r="67" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CX67" s="4"/>
       <c r="CY67" s="4"/>
       <c r="CZ67" s="4"/>
       <c r="DA67" s="4"/>
+      <c r="DB67" s="4"/>
     </row>
     <row r="68" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX68" s="4"/>
       <c r="CY68" s="4"/>
       <c r="CZ68" s="4"/>
       <c r="DA68" s="4"/>
+      <c r="DB68" s="4"/>
     </row>
     <row r="69" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="17"/>
@@ -9562,10 +9617,13 @@
       <c r="CU69" s="21"/>
       <c r="CV69" s="21"/>
       <c r="CW69" s="21"/>
-      <c r="CX69" s="22"/>
+      <c r="CX69" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="CY69" s="22"/>
       <c r="CZ69" s="22"/>
       <c r="DA69" s="22"/>
+      <c r="DB69" s="22"/>
     </row>
     <row r="70" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
@@ -9871,17 +9929,20 @@
       <c r="CW70" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX70" s="23"/>
+      <c r="CX70" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY70" s="23"/>
       <c r="CZ70" s="23"/>
       <c r="DA70" s="23"/>
+      <c r="DB70" s="23"/>
     </row>
     <row r="71" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6"/>
-      <c r="CX71" s="4"/>
       <c r="CY71" s="4"/>
       <c r="CZ71" s="4"/>
       <c r="DA71" s="4"/>
+      <c r="DB71" s="4"/>
     </row>
     <row r="72" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
@@ -10187,11 +10248,13 @@
       <c r="CW72" s="16">
         <v>3.3526103727812</v>
       </c>
-      <c r="CX72" s="18"/>
+      <c r="CX72" s="16">
+        <v>0.96160955151842131</v>
+      </c>
       <c r="CY72" s="18"/>
       <c r="CZ72" s="18"/>
       <c r="DA72" s="18"/>
-      <c r="DB72" s="8"/>
+      <c r="DB72" s="18"/>
       <c r="DC72" s="8"/>
       <c r="DD72" s="8"/>
       <c r="DE72" s="8"/>
@@ -10566,11 +10629,13 @@
       <c r="CW73" s="16">
         <v>5.0091273706273967</v>
       </c>
-      <c r="CX73" s="18"/>
+      <c r="CX73" s="16">
+        <v>5.3799531408605077</v>
+      </c>
       <c r="CY73" s="18"/>
       <c r="CZ73" s="18"/>
       <c r="DA73" s="18"/>
-      <c r="DB73" s="8"/>
+      <c r="DB73" s="18"/>
       <c r="DC73" s="8"/>
       <c r="DD73" s="8"/>
       <c r="DE73" s="8"/>
@@ -10945,11 +11010,13 @@
       <c r="CW74" s="16">
         <v>3.9751287962338324</v>
       </c>
-      <c r="CX74" s="18"/>
+      <c r="CX74" s="16">
+        <v>1.5283034049306821</v>
+      </c>
       <c r="CY74" s="18"/>
       <c r="CZ74" s="18"/>
       <c r="DA74" s="18"/>
-      <c r="DB74" s="8"/>
+      <c r="DB74" s="18"/>
       <c r="DC74" s="8"/>
       <c r="DD74" s="8"/>
       <c r="DE74" s="8"/>
@@ -11121,11 +11188,11 @@
       <c r="CU75" s="8"/>
       <c r="CV75" s="8"/>
       <c r="CW75" s="8"/>
-      <c r="CX75" s="7"/>
+      <c r="CX75" s="8"/>
       <c r="CY75" s="7"/>
       <c r="CZ75" s="7"/>
       <c r="DA75" s="7"/>
-      <c r="DB75" s="8"/>
+      <c r="DB75" s="7"/>
       <c r="DC75" s="8"/>
       <c r="DD75" s="8"/>
       <c r="DE75" s="8"/>
@@ -11500,11 +11567,13 @@
       <c r="CW76" s="16">
         <v>4.6831516963061262</v>
       </c>
-      <c r="CX76" s="18"/>
+      <c r="CX76" s="16">
+        <v>4.580023154106442</v>
+      </c>
       <c r="CY76" s="18"/>
       <c r="CZ76" s="18"/>
       <c r="DA76" s="18"/>
-      <c r="DB76" s="8"/>
+      <c r="DB76" s="18"/>
       <c r="DC76" s="8"/>
       <c r="DD76" s="8"/>
       <c r="DE76" s="8"/>
@@ -11677,19 +11746,20 @@
       <c r="CU77" s="10"/>
       <c r="CV77" s="10"/>
       <c r="CW77" s="10"/>
-      <c r="CX77" s="24"/>
+      <c r="CX77" s="10"/>
       <c r="CY77" s="24"/>
       <c r="CZ77" s="24"/>
       <c r="DA77" s="24"/>
+      <c r="DB77" s="24"/>
     </row>
     <row r="78" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A78" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CX78" s="4"/>
       <c r="CY78" s="4"/>
       <c r="CZ78" s="4"/>
       <c r="DA78" s="4"/>
+      <c r="DB78" s="4"/>
     </row>
     <row r="79" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B79" s="8"/>
@@ -11792,11 +11862,11 @@
       <c r="CU79" s="8"/>
       <c r="CV79" s="8"/>
       <c r="CW79" s="8"/>
-      <c r="CX79" s="7"/>
+      <c r="CX79" s="8"/>
       <c r="CY79" s="7"/>
       <c r="CZ79" s="7"/>
       <c r="DA79" s="7"/>
-      <c r="DB79" s="8"/>
+      <c r="DB79" s="7"/>
       <c r="DC79" s="8"/>
       <c r="DD79" s="8"/>
       <c r="DE79" s="8"/>
@@ -12050,7 +12120,7 @@
     </row>
     <row r="82" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="84" spans="1:179" x14ac:dyDescent="0.2">
@@ -12060,7 +12130,7 @@
     </row>
     <row r="85" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86" spans="1:179" x14ac:dyDescent="0.2">
@@ -12226,6 +12296,9 @@
       <c r="CY88" s="21"/>
       <c r="CZ88" s="21"/>
       <c r="DA88" s="21"/>
+      <c r="DB88" s="21">
+        <v>2026</v>
+      </c>
     </row>
     <row r="89" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
@@ -12542,6 +12615,9 @@
       </c>
       <c r="DA89" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB89" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -12863,7 +12939,9 @@
       <c r="DA91" s="16">
         <v>127.93098047054909</v>
       </c>
-      <c r="DB91" s="8"/>
+      <c r="DB91" s="16">
+        <v>127.77263068059337</v>
+      </c>
       <c r="DC91" s="8"/>
       <c r="DD91" s="8"/>
       <c r="DE91" s="8"/>
@@ -13254,7 +13332,9 @@
       <c r="DA92" s="16">
         <v>118.28449377457974</v>
       </c>
-      <c r="DB92" s="8"/>
+      <c r="DB92" s="16">
+        <v>121.39518455091773</v>
+      </c>
       <c r="DC92" s="8"/>
       <c r="DD92" s="8"/>
       <c r="DE92" s="8"/>
@@ -13645,7 +13725,9 @@
       <c r="DA93" s="16">
         <v>105.59105122264501</v>
       </c>
-      <c r="DB93" s="8"/>
+      <c r="DB93" s="16">
+        <v>109.51038199340204</v>
+      </c>
       <c r="DC93" s="8"/>
       <c r="DD93" s="8"/>
       <c r="DE93" s="8"/>
@@ -14216,7 +14298,9 @@
       <c r="DA95" s="16">
         <v>119.68532274749791</v>
       </c>
-      <c r="DB95" s="8"/>
+      <c r="DB95" s="16">
+        <v>121.96523220734346</v>
+      </c>
       <c r="DC95" s="8"/>
       <c r="DD95" s="8"/>
       <c r="DE95" s="8"/>
@@ -14397,6 +14481,7 @@
       <c r="CY96" s="10"/>
       <c r="CZ96" s="10"/>
       <c r="DA96" s="10"/>
+      <c r="DB96" s="10"/>
     </row>
     <row r="97" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A97" s="11" t="s">
@@ -14415,7 +14500,7 @@
     </row>
     <row r="102" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104" spans="1:179" x14ac:dyDescent="0.2">
@@ -14425,7 +14510,7 @@
     </row>
     <row r="105" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="106" spans="1:179" x14ac:dyDescent="0.2">
@@ -14591,6 +14676,9 @@
       <c r="CY108" s="21"/>
       <c r="CZ108" s="21"/>
       <c r="DA108" s="21"/>
+      <c r="DB108" s="21">
+        <v>2026</v>
+      </c>
     </row>
     <row r="109" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
@@ -14907,6 +14995,9 @@
       </c>
       <c r="DA109" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB109" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -15228,7 +15319,9 @@
       <c r="DA111" s="16">
         <v>19.086200647639398</v>
       </c>
-      <c r="DB111" s="8"/>
+      <c r="DB111" s="16">
+        <v>15.470198151773213</v>
+      </c>
       <c r="DC111" s="8"/>
       <c r="DD111" s="8"/>
       <c r="DE111" s="8"/>
@@ -15619,7 +15712,9 @@
       <c r="DA112" s="16">
         <v>78.678221606561166</v>
       </c>
-      <c r="DB112" s="8"/>
+      <c r="DB112" s="16">
+        <v>81.721551031899892</v>
+      </c>
       <c r="DC112" s="8"/>
       <c r="DD112" s="8"/>
       <c r="DE112" s="8"/>
@@ -16010,7 +16105,9 @@
       <c r="DA113" s="16">
         <v>2.2355777457994339</v>
       </c>
-      <c r="DB113" s="8"/>
+      <c r="DB113" s="16">
+        <v>2.8082508163268942</v>
+      </c>
       <c r="DC113" s="8"/>
       <c r="DD113" s="8"/>
       <c r="DE113" s="8"/>
@@ -16581,7 +16678,9 @@
       <c r="DA115" s="16">
         <v>100</v>
       </c>
-      <c r="DB115" s="8"/>
+      <c r="DB115" s="16">
+        <v>100</v>
+      </c>
       <c r="DC115" s="8"/>
       <c r="DD115" s="8"/>
       <c r="DE115" s="8"/>
@@ -16762,6 +16861,7 @@
       <c r="CY116" s="10"/>
       <c r="CZ116" s="10"/>
       <c r="DA116" s="10"/>
+      <c r="DB116" s="10"/>
     </row>
     <row r="117" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A117" s="11" t="s">
@@ -17140,7 +17240,7 @@
     </row>
     <row r="122" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="124" spans="1:179" x14ac:dyDescent="0.2">
@@ -17150,7 +17250,7 @@
     </row>
     <row r="125" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="126" spans="1:179" x14ac:dyDescent="0.2">
@@ -17316,6 +17416,9 @@
       <c r="CY128" s="21"/>
       <c r="CZ128" s="21"/>
       <c r="DA128" s="21"/>
+      <c r="DB128" s="21">
+        <v>2026</v>
+      </c>
     </row>
     <row r="129" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
@@ -17632,6 +17735,9 @@
       </c>
       <c r="DA129" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB129" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -17953,7 +18059,9 @@
       <c r="DA131" s="16">
         <v>17.856019520323311</v>
       </c>
-      <c r="DB131" s="8"/>
+      <c r="DB131" s="16">
+        <v>14.76706161424611</v>
+      </c>
       <c r="DC131" s="8"/>
       <c r="DD131" s="8"/>
       <c r="DE131" s="8"/>
@@ -18344,7 +18452,9 @@
       <c r="DA132" s="16">
         <v>79.609998281990727</v>
       </c>
-      <c r="DB132" s="8"/>
+      <c r="DB132" s="16">
+        <v>82.105299191413323</v>
+      </c>
       <c r="DC132" s="8"/>
       <c r="DD132" s="8"/>
       <c r="DE132" s="8"/>
@@ -18735,7 +18845,9 @@
       <c r="DA133" s="16">
         <v>2.5339821976859636</v>
       </c>
-      <c r="DB133" s="8"/>
+      <c r="DB133" s="16">
+        <v>3.1276391943405653</v>
+      </c>
       <c r="DC133" s="8"/>
       <c r="DD133" s="8"/>
       <c r="DE133" s="8"/>
@@ -19306,7 +19418,9 @@
       <c r="DA135" s="16">
         <v>100</v>
       </c>
-      <c r="DB135" s="8"/>
+      <c r="DB135" s="16">
+        <v>100</v>
+      </c>
       <c r="DC135" s="8"/>
       <c r="DD135" s="8"/>
       <c r="DE135" s="8"/>
@@ -19487,6 +19601,7 @@
       <c r="CY136" s="10"/>
       <c r="CZ136" s="10"/>
       <c r="DA136" s="10"/>
+      <c r="DB136" s="10"/>
     </row>
     <row r="137" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A137" s="11" t="s">
@@ -19599,7 +19714,7 @@
       <c r="CY138" s="14"/>
       <c r="CZ138" s="14"/>
       <c r="DA138" s="14"/>
-      <c r="DB138" s="13"/>
+      <c r="DB138" s="14"/>
       <c r="DC138" s="13"/>
       <c r="DD138" s="13"/>
       <c r="DE138" s="13"/>
@@ -19682,6 +19797,7 @@
       <c r="CY139" s="6"/>
       <c r="CZ139" s="6"/>
       <c r="DA139" s="6"/>
+      <c r="DB139" s="6"/>
     </row>
     <row r="140" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT140" s="6"/>
@@ -19691,6 +19807,7 @@
       <c r="CY140" s="6"/>
       <c r="CZ140" s="6"/>
       <c r="DA140" s="6"/>
+      <c r="DB140" s="6"/>
     </row>
     <row r="141" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT141" s="6"/>
@@ -19716,9 +19833,9 @@
   <pageSetup paperSize="9" scale="43" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="40" max="81" man="1"/>
-    <brk id="80" max="81" man="1"/>
-    <brk id="99" max="81" man="1"/>
+    <brk id="40" max="105" man="1"/>
+    <brk id="80" max="105" man="1"/>
+    <brk id="99" max="105" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-13TRD_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-13TRD_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF82A430-A3B6-4809-ADBA-03A8B71168F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4181FC08-137C-40DC-8899-0315502EFD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -353,7 +353,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">TRD!$A$1:$DB$138</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">TRD!$A$1:$DC$138</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -527,7 +527,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="55">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -685,13 +685,13 @@
     <t>Table 14.7 Gross Value Added in Wholesale and Retail Trade; Repair of Motor Vehicles and Motorcycles, by Industry</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>As of August 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
 </sst>
 </file>
@@ -1194,8 +1194,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="59.28515625" style="3" customWidth="1"/>
-    <col min="2" max="106" width="13" style="3" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="3"/>
+    <col min="2" max="107" width="13" style="3" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -1389,6 +1389,7 @@
       <c r="DB9" s="21">
         <v>2026</v>
       </c>
+      <c r="DC9" s="21"/>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1708,6 +1709,9 @@
       </c>
       <c r="DB10" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2030,9 +2034,11 @@
         <v>287839.75868115516</v>
       </c>
       <c r="DB12" s="19">
-        <v>178771.70160681123</v>
-      </c>
-      <c r="DC12" s="8"/>
+        <v>179254.78501867625</v>
+      </c>
+      <c r="DC12" s="19">
+        <v>184179.25649390288</v>
+      </c>
       <c r="DD12" s="8"/>
       <c r="DE12" s="8"/>
       <c r="DF12" s="8"/>
@@ -2423,9 +2429,11 @@
         <v>1186549.4206410318</v>
       </c>
       <c r="DB13" s="19">
-        <v>944364.16344454163</v>
-      </c>
-      <c r="DC13" s="8"/>
+        <v>945717.98478798452</v>
+      </c>
+      <c r="DC13" s="19">
+        <v>1164537.838717663</v>
+      </c>
       <c r="DD13" s="8"/>
       <c r="DE13" s="8"/>
       <c r="DF13" s="8"/>
@@ -2816,9 +2824,11 @@
         <v>33714.837790068879</v>
       </c>
       <c r="DB14" s="19">
-        <v>32451.80003825172</v>
-      </c>
-      <c r="DC14" s="8"/>
+        <v>32045.393999431384</v>
+      </c>
+      <c r="DC14" s="19">
+        <v>18916.691014040342</v>
+      </c>
       <c r="DD14" s="8"/>
       <c r="DE14" s="8"/>
       <c r="DF14" s="8"/>
@@ -3389,9 +3399,11 @@
         <v>1508104.0171122558</v>
       </c>
       <c r="DB16" s="20">
-        <v>1155587.6650896047</v>
-      </c>
-      <c r="DC16" s="8"/>
+        <v>1157018.163806092</v>
+      </c>
+      <c r="DC16" s="20">
+        <v>1367633.7862256062</v>
+      </c>
       <c r="DD16" s="8"/>
       <c r="DE16" s="8"/>
       <c r="DF16" s="8"/>
@@ -3572,6 +3584,7 @@
       <c r="CZ17" s="10"/>
       <c r="DA17" s="10"/>
       <c r="DB17" s="10"/>
+      <c r="DC17" s="10"/>
     </row>
     <row r="18" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
@@ -3950,7 +3963,7 @@
     </row>
     <row r="23" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:179" x14ac:dyDescent="0.2">
@@ -3960,7 +3973,7 @@
     </row>
     <row r="26" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:179" x14ac:dyDescent="0.2">
@@ -4129,6 +4142,7 @@
       <c r="DB29" s="21">
         <v>2026</v>
       </c>
+      <c r="DC29" s="21"/>
     </row>
     <row r="30" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
@@ -4448,6 +4462,9 @@
       </c>
       <c r="DB30" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC30" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -4770,9 +4787,11 @@
         <v>224996.1327759999</v>
       </c>
       <c r="DB32" s="19">
-        <v>139913.92417497106</v>
-      </c>
-      <c r="DC32" s="8"/>
+        <v>140532.943771388</v>
+      </c>
+      <c r="DC32" s="19">
+        <v>148146.26887574786</v>
+      </c>
       <c r="DD32" s="8"/>
       <c r="DE32" s="8"/>
       <c r="DF32" s="8"/>
@@ -5163,9 +5182,11 @@
         <v>1003131.8415263239</v>
       </c>
       <c r="DB33" s="19">
-        <v>777925.55523356819</v>
-      </c>
-      <c r="DC33" s="8"/>
+        <v>778986.89383085899</v>
+      </c>
+      <c r="DC33" s="19">
+        <v>887464.2801587896</v>
+      </c>
       <c r="DD33" s="8"/>
       <c r="DE33" s="8"/>
       <c r="DF33" s="8"/>
@@ -5556,9 +5577,11 @@
         <v>31929.635513315559</v>
       </c>
       <c r="DB34" s="19">
-        <v>29633.537430457443</v>
-      </c>
-      <c r="DC34" s="8"/>
+        <v>29251.357406436691</v>
+      </c>
+      <c r="DC34" s="19">
+        <v>18053.476017957139</v>
+      </c>
       <c r="DD34" s="8"/>
       <c r="DE34" s="8"/>
       <c r="DF34" s="8"/>
@@ -5738,7 +5761,7 @@
       <c r="CZ35" s="20"/>
       <c r="DA35" s="20"/>
       <c r="DB35" s="20"/>
-      <c r="DC35" s="8"/>
+      <c r="DC35" s="20"/>
       <c r="DD35" s="8"/>
       <c r="DE35" s="8"/>
       <c r="DF35" s="8"/>
@@ -6129,9 +6152,11 @@
         <v>1260057.6098156394</v>
       </c>
       <c r="DB36" s="20">
-        <v>947473.01683899667</v>
-      </c>
-      <c r="DC36" s="8"/>
+        <v>948771.19500868372</v>
+      </c>
+      <c r="DC36" s="20">
+        <v>1053664.0250524946</v>
+      </c>
       <c r="DD36" s="8"/>
       <c r="DE36" s="8"/>
       <c r="DF36" s="8"/>
@@ -6312,6 +6337,7 @@
       <c r="CZ37" s="10"/>
       <c r="DA37" s="10"/>
       <c r="DB37" s="10"/>
+      <c r="DC37" s="10"/>
     </row>
     <row r="38" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
@@ -6692,16 +6718,18 @@
       <c r="CZ42" s="4"/>
       <c r="DA42" s="4"/>
       <c r="DB42" s="4"/>
+      <c r="DC42" s="4"/>
     </row>
     <row r="43" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CX43" s="4"/>
       <c r="CY43" s="4"/>
       <c r="CZ43" s="4"/>
       <c r="DA43" s="4"/>
       <c r="DB43" s="4"/>
+      <c r="DC43" s="4"/>
     </row>
     <row r="44" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT44" s="6"/>
@@ -6713,6 +6741,7 @@
       <c r="CZ44" s="4"/>
       <c r="DA44" s="4"/>
       <c r="DB44" s="4"/>
+      <c r="DC44" s="4"/>
     </row>
     <row r="45" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
@@ -6723,16 +6752,18 @@
       <c r="CZ45" s="4"/>
       <c r="DA45" s="4"/>
       <c r="DB45" s="4"/>
+      <c r="DC45" s="4"/>
     </row>
     <row r="46" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CX46" s="4"/>
       <c r="CY46" s="4"/>
       <c r="CZ46" s="4"/>
       <c r="DA46" s="4"/>
       <c r="DB46" s="4"/>
+      <c r="DC46" s="4"/>
     </row>
     <row r="47" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
@@ -6743,13 +6774,13 @@
       <c r="CZ47" s="4"/>
       <c r="DA47" s="4"/>
       <c r="DB47" s="4"/>
+      <c r="DC47" s="4"/>
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
-      <c r="CX48" s="4"/>
-      <c r="CY48" s="4"/>
       <c r="CZ48" s="4"/>
       <c r="DA48" s="4"/>
       <c r="DB48" s="4"/>
+      <c r="DC48" s="4"/>
     </row>
     <row r="49" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="17"/>
@@ -6904,12 +6935,13 @@
       <c r="CV49" s="21"/>
       <c r="CW49" s="21"/>
       <c r="CX49" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="CY49" s="22"/>
+        <v>52</v>
+      </c>
+      <c r="CY49" s="21"/>
       <c r="CZ49" s="22"/>
       <c r="DA49" s="22"/>
       <c r="DB49" s="22"/>
+      <c r="DC49" s="22"/>
     </row>
     <row r="50" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
@@ -7218,17 +7250,20 @@
       <c r="CX50" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY50" s="23"/>
+      <c r="CY50" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ50" s="23"/>
       <c r="DA50" s="23"/>
       <c r="DB50" s="23"/>
+      <c r="DC50" s="23"/>
     </row>
     <row r="51" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6"/>
-      <c r="CY51" s="4"/>
       <c r="CZ51" s="4"/>
       <c r="DA51" s="4"/>
       <c r="DB51" s="4"/>
+      <c r="DC51" s="4"/>
     </row>
     <row r="52" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
@@ -7535,13 +7570,15 @@
         <v>5.9335483656549002</v>
       </c>
       <c r="CX52" s="16">
-        <v>2.9665056029162429</v>
-      </c>
-      <c r="CY52" s="18"/>
+        <v>3.2447454495328998</v>
+      </c>
+      <c r="CY52" s="16">
+        <v>14.544821803293701</v>
+      </c>
       <c r="CZ52" s="18"/>
       <c r="DA52" s="18"/>
       <c r="DB52" s="18"/>
-      <c r="DC52" s="8"/>
+      <c r="DC52" s="18"/>
       <c r="DD52" s="8"/>
       <c r="DE52" s="8"/>
       <c r="DF52" s="8"/>
@@ -7916,13 +7953,15 @@
         <v>5.7696026255762263</v>
       </c>
       <c r="CX53" s="16">
-        <v>7.5988568647099299</v>
-      </c>
-      <c r="CY53" s="18"/>
+        <v>7.7531084072739702</v>
+      </c>
+      <c r="CY53" s="16">
+        <v>12.618431536085509</v>
+      </c>
       <c r="CZ53" s="18"/>
       <c r="DA53" s="18"/>
       <c r="DB53" s="18"/>
-      <c r="DC53" s="8"/>
+      <c r="DC53" s="18"/>
       <c r="DD53" s="8"/>
       <c r="DE53" s="8"/>
       <c r="DF53" s="8"/>
@@ -8297,13 +8336,15 @@
         <v>5.6290508255864466</v>
       </c>
       <c r="CX54" s="16">
-        <v>2.9138333701217647</v>
-      </c>
-      <c r="CY54" s="18"/>
+        <v>1.6250049134423961</v>
+      </c>
+      <c r="CY54" s="16">
+        <v>-10.272665027353725</v>
+      </c>
       <c r="CZ54" s="18"/>
       <c r="DA54" s="18"/>
       <c r="DB54" s="18"/>
-      <c r="DC54" s="8"/>
+      <c r="DC54" s="18"/>
       <c r="DD54" s="8"/>
       <c r="DE54" s="8"/>
       <c r="DF54" s="8"/>
@@ -8475,11 +8516,11 @@
       <c r="CV55" s="8"/>
       <c r="CW55" s="8"/>
       <c r="CX55" s="8"/>
-      <c r="CY55" s="7"/>
+      <c r="CY55" s="8"/>
       <c r="CZ55" s="7"/>
       <c r="DA55" s="7"/>
       <c r="DB55" s="7"/>
-      <c r="DC55" s="8"/>
+      <c r="DC55" s="7"/>
       <c r="DD55" s="8"/>
       <c r="DE55" s="8"/>
       <c r="DF55" s="8"/>
@@ -8854,13 +8895,15 @@
         <v>5.7977063512495874</v>
       </c>
       <c r="CX56" s="16">
-        <v>6.7196687318755295</v>
-      </c>
-      <c r="CY56" s="18"/>
+        <v>6.8517767092768338</v>
+      </c>
+      <c r="CY56" s="16">
+        <v>12.476276319443258</v>
+      </c>
       <c r="CZ56" s="18"/>
       <c r="DA56" s="18"/>
       <c r="DB56" s="18"/>
-      <c r="DC56" s="8"/>
+      <c r="DC56" s="18"/>
       <c r="DD56" s="8"/>
       <c r="DE56" s="8"/>
       <c r="DF56" s="8"/>
@@ -9033,19 +9076,20 @@
       <c r="CV57" s="10"/>
       <c r="CW57" s="10"/>
       <c r="CX57" s="10"/>
-      <c r="CY57" s="24"/>
+      <c r="CY57" s="10"/>
       <c r="CZ57" s="24"/>
       <c r="DA57" s="24"/>
       <c r="DB57" s="24"/>
+      <c r="DC57" s="24"/>
     </row>
     <row r="58" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A58" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CY58" s="4"/>
       <c r="CZ58" s="4"/>
       <c r="DA58" s="4"/>
       <c r="DB58" s="4"/>
+      <c r="DC58" s="4"/>
     </row>
     <row r="59" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="8"/>
@@ -9149,11 +9193,11 @@
       <c r="CV59" s="8"/>
       <c r="CW59" s="8"/>
       <c r="CX59" s="8"/>
-      <c r="CY59" s="7"/>
+      <c r="CY59" s="8"/>
       <c r="CZ59" s="7"/>
       <c r="DA59" s="7"/>
       <c r="DB59" s="7"/>
-      <c r="DC59" s="8"/>
+      <c r="DC59" s="7"/>
       <c r="DD59" s="8"/>
       <c r="DE59" s="8"/>
       <c r="DF59" s="8"/>
@@ -9325,11 +9369,11 @@
       <c r="CV60" s="8"/>
       <c r="CW60" s="8"/>
       <c r="CX60" s="8"/>
-      <c r="CY60" s="7"/>
+      <c r="CY60" s="8"/>
       <c r="CZ60" s="7"/>
       <c r="DA60" s="7"/>
       <c r="DB60" s="7"/>
-      <c r="DC60" s="8"/>
+      <c r="DC60" s="7"/>
       <c r="DD60" s="8"/>
       <c r="DE60" s="8"/>
       <c r="DF60" s="8"/>
@@ -9403,67 +9447,67 @@
       <c r="A61" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="CY61" s="4"/>
       <c r="CZ61" s="4"/>
       <c r="DA61" s="4"/>
       <c r="DB61" s="4"/>
+      <c r="DC61" s="4"/>
     </row>
     <row r="62" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="CY62" s="4"/>
       <c r="CZ62" s="4"/>
       <c r="DA62" s="4"/>
       <c r="DB62" s="4"/>
+      <c r="DC62" s="4"/>
     </row>
     <row r="63" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="CY63" s="4"/>
+        <v>53</v>
+      </c>
       <c r="CZ63" s="4"/>
       <c r="DA63" s="4"/>
       <c r="DB63" s="4"/>
+      <c r="DC63" s="4"/>
     </row>
     <row r="64" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY64" s="4"/>
       <c r="CZ64" s="4"/>
       <c r="DA64" s="4"/>
       <c r="DB64" s="4"/>
+      <c r="DC64" s="4"/>
     </row>
     <row r="65" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="CY65" s="4"/>
       <c r="CZ65" s="4"/>
       <c r="DA65" s="4"/>
       <c r="DB65" s="4"/>
+      <c r="DC65" s="4"/>
     </row>
     <row r="66" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="CY66" s="4"/>
+        <v>54</v>
+      </c>
       <c r="CZ66" s="4"/>
       <c r="DA66" s="4"/>
       <c r="DB66" s="4"/>
+      <c r="DC66" s="4"/>
     </row>
     <row r="67" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CY67" s="4"/>
       <c r="CZ67" s="4"/>
       <c r="DA67" s="4"/>
       <c r="DB67" s="4"/>
+      <c r="DC67" s="4"/>
     </row>
     <row r="68" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY68" s="4"/>
       <c r="CZ68" s="4"/>
       <c r="DA68" s="4"/>
       <c r="DB68" s="4"/>
+      <c r="DC68" s="4"/>
     </row>
     <row r="69" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="17"/>
@@ -9618,12 +9662,13 @@
       <c r="CV69" s="21"/>
       <c r="CW69" s="21"/>
       <c r="CX69" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="CY69" s="22"/>
+        <v>52</v>
+      </c>
+      <c r="CY69" s="21"/>
       <c r="CZ69" s="22"/>
       <c r="DA69" s="22"/>
       <c r="DB69" s="22"/>
+      <c r="DC69" s="22"/>
     </row>
     <row r="70" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
@@ -9932,17 +9977,20 @@
       <c r="CX70" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY70" s="23"/>
+      <c r="CY70" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ70" s="23"/>
       <c r="DA70" s="23"/>
       <c r="DB70" s="23"/>
+      <c r="DC70" s="23"/>
     </row>
     <row r="71" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6"/>
-      <c r="CY71" s="4"/>
       <c r="CZ71" s="4"/>
       <c r="DA71" s="4"/>
       <c r="DB71" s="4"/>
+      <c r="DC71" s="4"/>
     </row>
     <row r="72" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
@@ -10249,13 +10297,15 @@
         <v>3.3526103727812</v>
       </c>
       <c r="CX72" s="16">
-        <v>0.96160955151842131</v>
-      </c>
-      <c r="CY72" s="18"/>
+        <v>1.4082928617515762</v>
+      </c>
+      <c r="CY72" s="16">
+        <v>13.334990160600071</v>
+      </c>
       <c r="CZ72" s="18"/>
       <c r="DA72" s="18"/>
       <c r="DB72" s="18"/>
-      <c r="DC72" s="8"/>
+      <c r="DC72" s="18"/>
       <c r="DD72" s="8"/>
       <c r="DE72" s="8"/>
       <c r="DF72" s="8"/>
@@ -10630,13 +10680,15 @@
         <v>5.0091273706273967</v>
       </c>
       <c r="CX73" s="16">
-        <v>5.3799531408605077</v>
-      </c>
-      <c r="CY73" s="18"/>
+        <v>5.5237250106707307</v>
+      </c>
+      <c r="CY73" s="16">
+        <v>3.5638234002227449</v>
+      </c>
       <c r="CZ73" s="18"/>
       <c r="DA73" s="18"/>
       <c r="DB73" s="18"/>
-      <c r="DC73" s="8"/>
+      <c r="DC73" s="18"/>
       <c r="DD73" s="8"/>
       <c r="DE73" s="8"/>
       <c r="DF73" s="8"/>
@@ -11011,13 +11063,15 @@
         <v>3.9751287962338324</v>
       </c>
       <c r="CX74" s="16">
-        <v>1.5283034049306821</v>
-      </c>
-      <c r="CY74" s="18"/>
+        <v>0.21890558075456568</v>
+      </c>
+      <c r="CY74" s="16">
+        <v>-10.247742411769536</v>
+      </c>
       <c r="CZ74" s="18"/>
       <c r="DA74" s="18"/>
       <c r="DB74" s="18"/>
-      <c r="DC74" s="8"/>
+      <c r="DC74" s="18"/>
       <c r="DD74" s="8"/>
       <c r="DE74" s="8"/>
       <c r="DF74" s="8"/>
@@ -11189,11 +11243,11 @@
       <c r="CV75" s="8"/>
       <c r="CW75" s="8"/>
       <c r="CX75" s="8"/>
-      <c r="CY75" s="7"/>
+      <c r="CY75" s="8"/>
       <c r="CZ75" s="7"/>
       <c r="DA75" s="7"/>
       <c r="DB75" s="7"/>
-      <c r="DC75" s="8"/>
+      <c r="DC75" s="7"/>
       <c r="DD75" s="8"/>
       <c r="DE75" s="8"/>
       <c r="DF75" s="8"/>
@@ -11568,13 +11622,15 @@
         <v>4.6831516963061262</v>
       </c>
       <c r="CX76" s="16">
-        <v>4.580023154106442</v>
-      </c>
-      <c r="CY76" s="18"/>
+        <v>4.7233132538044345</v>
+      </c>
+      <c r="CY76" s="16">
+        <v>4.5555574571476143</v>
+      </c>
       <c r="CZ76" s="18"/>
       <c r="DA76" s="18"/>
       <c r="DB76" s="18"/>
-      <c r="DC76" s="8"/>
+      <c r="DC76" s="18"/>
       <c r="DD76" s="8"/>
       <c r="DE76" s="8"/>
       <c r="DF76" s="8"/>
@@ -11747,19 +11803,20 @@
       <c r="CV77" s="10"/>
       <c r="CW77" s="10"/>
       <c r="CX77" s="10"/>
-      <c r="CY77" s="24"/>
+      <c r="CY77" s="10"/>
       <c r="CZ77" s="24"/>
       <c r="DA77" s="24"/>
       <c r="DB77" s="24"/>
+      <c r="DC77" s="24"/>
     </row>
     <row r="78" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A78" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CY78" s="4"/>
       <c r="CZ78" s="4"/>
       <c r="DA78" s="4"/>
       <c r="DB78" s="4"/>
+      <c r="DC78" s="4"/>
     </row>
     <row r="79" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B79" s="8"/>
@@ -11863,11 +11920,11 @@
       <c r="CV79" s="8"/>
       <c r="CW79" s="8"/>
       <c r="CX79" s="8"/>
-      <c r="CY79" s="7"/>
+      <c r="CY79" s="8"/>
       <c r="CZ79" s="7"/>
       <c r="DA79" s="7"/>
       <c r="DB79" s="7"/>
-      <c r="DC79" s="8"/>
+      <c r="DC79" s="7"/>
       <c r="DD79" s="8"/>
       <c r="DE79" s="8"/>
       <c r="DF79" s="8"/>
@@ -12120,7 +12177,7 @@
     </row>
     <row r="82" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84" spans="1:179" x14ac:dyDescent="0.2">
@@ -12130,7 +12187,7 @@
     </row>
     <row r="85" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86" spans="1:179" x14ac:dyDescent="0.2">
@@ -12299,6 +12356,7 @@
       <c r="DB88" s="21">
         <v>2026</v>
       </c>
+      <c r="DC88" s="21"/>
     </row>
     <row r="89" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
@@ -12618,6 +12676,9 @@
       </c>
       <c r="DB89" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC89" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -12940,9 +13001,11 @@
         <v>127.93098047054909</v>
       </c>
       <c r="DB91" s="16">
-        <v>127.77263068059337</v>
-      </c>
-      <c r="DC91" s="8"/>
+        <v>127.55356872782728</v>
+      </c>
+      <c r="DC91" s="16">
+        <v>124.32257517627821</v>
+      </c>
       <c r="DD91" s="8"/>
       <c r="DE91" s="8"/>
       <c r="DF91" s="8"/>
@@ -13333,9 +13396,11 @@
         <v>118.28449377457974</v>
       </c>
       <c r="DB92" s="16">
-        <v>121.39518455091773</v>
-      </c>
-      <c r="DC92" s="8"/>
+        <v>121.40358102010991</v>
+      </c>
+      <c r="DC92" s="16">
+        <v>131.22081246011365</v>
+      </c>
       <c r="DD92" s="8"/>
       <c r="DE92" s="8"/>
       <c r="DF92" s="8"/>
@@ -13726,9 +13791,11 @@
         <v>105.59105122264501</v>
       </c>
       <c r="DB93" s="16">
-        <v>109.51038199340204</v>
-      </c>
-      <c r="DC93" s="8"/>
+        <v>109.55181858459626</v>
+      </c>
+      <c r="DC93" s="16">
+        <v>104.7814337539463</v>
+      </c>
       <c r="DD93" s="8"/>
       <c r="DE93" s="8"/>
       <c r="DF93" s="8"/>
@@ -14299,9 +14366,11 @@
         <v>119.68532274749791</v>
       </c>
       <c r="DB95" s="16">
-        <v>121.96523220734346</v>
-      </c>
-      <c r="DC95" s="8"/>
+        <v>121.94912428760047</v>
+      </c>
+      <c r="DC95" s="16">
+        <v>129.79790082113408</v>
+      </c>
       <c r="DD95" s="8"/>
       <c r="DE95" s="8"/>
       <c r="DF95" s="8"/>
@@ -14482,6 +14551,7 @@
       <c r="CZ96" s="10"/>
       <c r="DA96" s="10"/>
       <c r="DB96" s="10"/>
+      <c r="DC96" s="10"/>
     </row>
     <row r="97" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A97" s="11" t="s">
@@ -14500,7 +14570,7 @@
     </row>
     <row r="102" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="104" spans="1:179" x14ac:dyDescent="0.2">
@@ -14510,7 +14580,7 @@
     </row>
     <row r="105" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="106" spans="1:179" x14ac:dyDescent="0.2">
@@ -14679,6 +14749,7 @@
       <c r="DB108" s="21">
         <v>2026</v>
       </c>
+      <c r="DC108" s="21"/>
     </row>
     <row r="109" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
@@ -14998,6 +15069,9 @@
       </c>
       <c r="DB109" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC109" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -15320,9 +15394,11 @@
         <v>19.086200647639398</v>
       </c>
       <c r="DB111" s="16">
-        <v>15.470198151773213</v>
-      </c>
-      <c r="DC111" s="8"/>
+        <v>15.492823762507335</v>
+      </c>
+      <c r="DC111" s="16">
+        <v>13.467001060437426</v>
+      </c>
       <c r="DD111" s="8"/>
       <c r="DE111" s="8"/>
       <c r="DF111" s="8"/>
@@ -15713,9 +15789,11 @@
         <v>78.678221606561166</v>
       </c>
       <c r="DB112" s="16">
-        <v>81.721551031899892</v>
-      </c>
-      <c r="DC112" s="8"/>
+        <v>81.737522743547885</v>
+      </c>
+      <c r="DC112" s="16">
+        <v>85.149829614223904</v>
+      </c>
       <c r="DD112" s="8"/>
       <c r="DE112" s="8"/>
       <c r="DF112" s="8"/>
@@ -16106,9 +16184,11 @@
         <v>2.2355777457994339</v>
       </c>
       <c r="DB113" s="16">
-        <v>2.8082508163268942</v>
-      </c>
-      <c r="DC113" s="8"/>
+        <v>2.7696534939447992</v>
+      </c>
+      <c r="DC113" s="16">
+        <v>1.3831693253386639</v>
+      </c>
       <c r="DD113" s="8"/>
       <c r="DE113" s="8"/>
       <c r="DF113" s="8"/>
@@ -16681,7 +16761,9 @@
       <c r="DB115" s="16">
         <v>100</v>
       </c>
-      <c r="DC115" s="8"/>
+      <c r="DC115" s="16">
+        <v>100</v>
+      </c>
       <c r="DD115" s="8"/>
       <c r="DE115" s="8"/>
       <c r="DF115" s="8"/>
@@ -16862,6 +16944,7 @@
       <c r="CZ116" s="10"/>
       <c r="DA116" s="10"/>
       <c r="DB116" s="10"/>
+      <c r="DC116" s="10"/>
     </row>
     <row r="117" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A117" s="11" t="s">
@@ -17240,7 +17323,7 @@
     </row>
     <row r="122" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="124" spans="1:179" x14ac:dyDescent="0.2">
@@ -17250,7 +17333,7 @@
     </row>
     <row r="125" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="126" spans="1:179" x14ac:dyDescent="0.2">
@@ -17419,6 +17502,7 @@
       <c r="DB128" s="21">
         <v>2026</v>
       </c>
+      <c r="DC128" s="21"/>
     </row>
     <row r="129" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
@@ -17738,6 +17822,9 @@
       </c>
       <c r="DB129" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC129" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -18060,9 +18147,11 @@
         <v>17.856019520323311</v>
       </c>
       <c r="DB131" s="16">
-        <v>14.76706161424611</v>
-      </c>
-      <c r="DC131" s="8"/>
+        <v>14.812100589763558</v>
+      </c>
+      <c r="DC131" s="16">
+        <v>14.060105057526954</v>
+      </c>
       <c r="DD131" s="8"/>
       <c r="DE131" s="8"/>
       <c r="DF131" s="8"/>
@@ -18453,9 +18542,11 @@
         <v>79.609998281990727</v>
       </c>
       <c r="DB132" s="16">
-        <v>82.105299191413323</v>
-      </c>
-      <c r="DC132" s="8"/>
+        <v>82.104821260275429</v>
+      </c>
+      <c r="DC132" s="16">
+        <v>84.226495263950511</v>
+      </c>
       <c r="DD132" s="8"/>
       <c r="DE132" s="8"/>
       <c r="DF132" s="8"/>
@@ -18846,9 +18937,11 @@
         <v>2.5339821976859636</v>
       </c>
       <c r="DB133" s="16">
-        <v>3.1276391943405653</v>
-      </c>
-      <c r="DC133" s="8"/>
+        <v>3.0830781499610098</v>
+      </c>
+      <c r="DC133" s="16">
+        <v>1.7133996785225438</v>
+      </c>
       <c r="DD133" s="8"/>
       <c r="DE133" s="8"/>
       <c r="DF133" s="8"/>
@@ -19421,7 +19514,9 @@
       <c r="DB135" s="16">
         <v>100</v>
       </c>
-      <c r="DC135" s="8"/>
+      <c r="DC135" s="16">
+        <v>100</v>
+      </c>
       <c r="DD135" s="8"/>
       <c r="DE135" s="8"/>
       <c r="DF135" s="8"/>
@@ -19602,6 +19697,7 @@
       <c r="CZ136" s="10"/>
       <c r="DA136" s="10"/>
       <c r="DB136" s="10"/>
+      <c r="DC136" s="10"/>
     </row>
     <row r="137" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A137" s="11" t="s">
@@ -19715,7 +19811,7 @@
       <c r="CZ138" s="14"/>
       <c r="DA138" s="14"/>
       <c r="DB138" s="14"/>
-      <c r="DC138" s="13"/>
+      <c r="DC138" s="14"/>
       <c r="DD138" s="13"/>
       <c r="DE138" s="13"/>
       <c r="DF138" s="13"/>
@@ -19798,6 +19894,7 @@
       <c r="CZ139" s="6"/>
       <c r="DA139" s="6"/>
       <c r="DB139" s="6"/>
+      <c r="DC139" s="6"/>
     </row>
     <row r="140" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT140" s="6"/>
@@ -19808,6 +19905,7 @@
       <c r="CZ140" s="6"/>
       <c r="DA140" s="6"/>
       <c r="DB140" s="6"/>
+      <c r="DC140" s="6"/>
     </row>
     <row r="141" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT141" s="6"/>
@@ -19817,15 +19915,13 @@
       <c r="CY141" s="6"/>
       <c r="CZ141" s="6"/>
       <c r="DA141" s="6"/>
+      <c r="DB141" s="6"/>
+      <c r="DC141" s="6"/>
     </row>
     <row r="142" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT142" s="6"/>
       <c r="CU142" s="6"/>
       <c r="CV142" s="6"/>
-      <c r="CX142" s="6"/>
-      <c r="CY142" s="6"/>
-      <c r="CZ142" s="6"/>
-      <c r="DA142" s="6"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -19833,9 +19929,9 @@
   <pageSetup paperSize="9" scale="43" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="40" max="105" man="1"/>
-    <brk id="80" max="105" man="1"/>
-    <brk id="99" max="105" man="1"/>
+    <brk id="40" max="106" man="1"/>
+    <brk id="80" max="106" man="1"/>
+    <brk id="99" max="106" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>